--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_19/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_19/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.99999996283002</v>
+        <v>99.99999998417366</v>
       </c>
       <c r="B2" t="n">
-        <v>170.8609815435492</v>
+        <v>120.0831143587765</v>
       </c>
       <c r="C2" t="n">
-        <v>48.78038333689555</v>
+        <v>45.43337187816507</v>
       </c>
       <c r="D2" t="n">
-        <v>5.455943934813428</v>
+        <v>6.274870359588562</v>
       </c>
       <c r="E2" t="n">
-        <v>3.365775878055661</v>
+        <v>2.219630150405139</v>
       </c>
       <c r="F2" t="n">
-        <v>15.40386090610055</v>
+        <v>15.67664493676537</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03236089516172423</v>
+        <v>0.03189740508594037</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8860275953268053</v>
+        <v>-0.8704727507589887</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9213073419492747</v>
+        <v>-0.9125292476190666</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9428309415267907</v>
+        <v>-0.9323873336576549</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.00105115915417854</v>
+        <v>-0.005741779658548348</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6220069727163737</v>
+        <v>-0.5874999998872373</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07679401313772481</v>
+        <v>-0.003644773417832842</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99.99999996283002</v>
+        <v>49.24175979582745</v>
       </c>
       <c r="B3" t="n">
-        <v>125.7187411590893</v>
+        <v>119.4426269482659</v>
       </c>
       <c r="C3" t="n">
-        <v>48.78038333689555</v>
+        <v>45.42603699289726</v>
       </c>
       <c r="D3" t="n">
-        <v>5.455943934813428</v>
+        <v>10.54809805488446</v>
       </c>
       <c r="E3" t="n">
-        <v>3.365775878055661</v>
+        <v>2.447699023964044</v>
       </c>
       <c r="F3" t="n">
-        <v>15.40386090610055</v>
+        <v>6.015365616621969</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03236089516172423</v>
+        <v>0.3924347892092494</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8860275953268053</v>
+        <v>-0.009437309486892665</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9213073419492747</v>
+        <v>-0.5755171435942383</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9428309415267907</v>
+        <v>-0.0009898024718170012</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.00105115915417854</v>
+        <v>-0.0007606489692424372</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6220069727163737</v>
+        <v>-0.2443131984687059</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.07679401313772481</v>
+        <v>-0.002044434813947699</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>47.29756891491404</v>
+        <v>99.99999998417366</v>
       </c>
       <c r="B4" t="n">
-        <v>134.1225766203304</v>
+        <v>94.58643661678437</v>
       </c>
       <c r="C4" t="n">
-        <v>48.78143490094609</v>
+        <v>45.43337187816507</v>
       </c>
       <c r="D4" t="n">
-        <v>10.33042855809284</v>
+        <v>6.274870359588562</v>
       </c>
       <c r="E4" t="n">
-        <v>3.19283784578212</v>
+        <v>2.219630150405139</v>
       </c>
       <c r="F4" t="n">
-        <v>5.734245309541487</v>
+        <v>15.67664493676537</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4666601237689672</v>
+        <v>0.03189740508594037</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.01255488900103432</v>
+        <v>-0.8704727507589887</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5742153085386033</v>
+        <v>-0.9125292476190666</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0004770411003151819</v>
+        <v>-0.9323873336576549</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0002660652267048286</v>
+        <v>-0.005741779658548348</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2283161378510675</v>
+        <v>-0.5874999998872373</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.07686582718642122</v>
+        <v>-0.003644773417832842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>76.11885735452552</v>
+        <v>77.94686815168055</v>
       </c>
       <c r="B5" t="n">
-        <v>166.7535351591882</v>
+        <v>139.9335251337733</v>
       </c>
       <c r="C5" t="n">
-        <v>49.19273447392982</v>
+        <v>45.65017662892971</v>
       </c>
       <c r="D5" t="n">
-        <v>8.017133950173031</v>
+        <v>8.564905435009431</v>
       </c>
       <c r="E5" t="n">
-        <v>3.162177354350016</v>
+        <v>2.503997785281321</v>
       </c>
       <c r="F5" t="n">
-        <v>10.15577693910436</v>
+        <v>10.70068167843999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08100953660746771</v>
+        <v>0.07343784570263401</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7539243319548887</v>
+        <v>-0.7375520667130948</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.853392995537411</v>
+        <v>-0.8456225883087027</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8419190342481386</v>
+        <v>-0.8280265570328723</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.004589143372653074</v>
+        <v>-0.02244168777024165</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4436131722016893</v>
+        <v>-0.4303714355807239</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1028951181963823</v>
+        <v>-0.05094762813011855</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>51.53190741629708</v>
+        <v>51.45560064864324</v>
       </c>
       <c r="B6" t="n">
-        <v>124.3614212204506</v>
+        <v>153.1610007492178</v>
       </c>
       <c r="C6" t="n">
-        <v>48.80213581539576</v>
+        <v>45.47170576674186</v>
       </c>
       <c r="D6" t="n">
-        <v>10.3463396438785</v>
+        <v>10.57916257215382</v>
       </c>
       <c r="E6" t="n">
-        <v>4.399115514469022</v>
+        <v>2.442163250240553</v>
       </c>
       <c r="F6" t="n">
-        <v>6.32661184530515</v>
+        <v>6.34075163988928</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3380269633796705</v>
+        <v>0.3329028606270558</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2327908902536525</v>
+        <v>-0.1177368452389642</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6474626262556527</v>
+        <v>-0.6082995896278709</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2852364426686467</v>
+        <v>-0.1404731636371966</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.06156391534808197</v>
+        <v>-0.00253790391517729</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.25994694171657</v>
+        <v>-0.2416211546215831</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07827954656716125</v>
+        <v>-0.01200853092549803</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>52.46051179087776</v>
+        <v>54.05376728319159</v>
       </c>
       <c r="B7" t="n">
-        <v>131.7736718411259</v>
+        <v>114.1592685231769</v>
       </c>
       <c r="C7" t="n">
-        <v>47.92673010034351</v>
+        <v>45.64380910810827</v>
       </c>
       <c r="D7" t="n">
-        <v>10.32709580192164</v>
+        <v>10.41118015433597</v>
       </c>
       <c r="E7" t="n">
-        <v>3.187002145692296</v>
+        <v>2.118888500977041</v>
       </c>
       <c r="F7" t="n">
-        <v>6.470756037366919</v>
+        <v>6.696723196809756</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3163155247241049</v>
+        <v>0.2767057436648609</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.271934238011434</v>
+        <v>-0.2471350299918263</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6610708476168831</v>
+        <v>-0.6542994253896874</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3332514053876971</v>
+        <v>-0.3061480179822356</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.05392008468005108</v>
+        <v>-0.02927521954678621</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2668836811462153</v>
+        <v>-0.2702681732583385</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07778159987745774</v>
+        <v>-0.04955835085998672</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66.298052473417</v>
+        <v>54.98638596397098</v>
       </c>
       <c r="B8" t="n">
-        <v>141.030907114516</v>
+        <v>110.8424459986467</v>
       </c>
       <c r="C8" t="n">
-        <v>48.79286482341865</v>
+        <v>45.42981118895121</v>
       </c>
       <c r="D8" t="n">
-        <v>8.879696931773179</v>
+        <v>10.11411164023449</v>
       </c>
       <c r="E8" t="n">
-        <v>4.261092349353362</v>
+        <v>2.031346515155589</v>
       </c>
       <c r="F8" t="n">
-        <v>8.399294514975141</v>
+        <v>6.755579942482278</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1324490164700008</v>
+        <v>0.258805887171378</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6333835220896655</v>
+        <v>-0.2843335665480269</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7995926611803575</v>
+        <v>-0.6672982236924316</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7319101954863375</v>
+        <v>-0.3513729196122248</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0001017998447677767</v>
+        <v>-0.001959095075193545</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3702510749356701</v>
+        <v>-0.2873978947297824</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.07764640637093606</v>
+        <v>-0.002867895771173495</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>58.30584419940558</v>
+        <v>74.15352149604716</v>
       </c>
       <c r="B9" t="n">
-        <v>178.7531573043674</v>
+        <v>117.9317493543343</v>
       </c>
       <c r="C9" t="n">
-        <v>48.80238810649685</v>
+        <v>45.42684341918272</v>
       </c>
       <c r="D9" t="n">
-        <v>9.635648993379689</v>
+        <v>9.124583135922324</v>
       </c>
       <c r="E9" t="n">
-        <v>2.550523396383945</v>
+        <v>2.39357750438355</v>
       </c>
       <c r="F9" t="n">
-        <v>7.192165419169064</v>
+        <v>10.01197270078534</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2123345195560851</v>
+        <v>0.087556145772825</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4665930248308795</v>
+        <v>-0.6968605703405235</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.732448586632943</v>
+        <v>-0.8270583224788791</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5590432850962354</v>
+        <v>-0.791831385688937</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.02504093546988549</v>
+        <v>-0.0662561448750101</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3105487218325985</v>
+        <v>-0.403343840659336</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07829677618376008</v>
+        <v>-0.002220382367138923</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>83.20875217775144</v>
+        <v>50.31096771837852</v>
       </c>
       <c r="B10" t="n">
-        <v>122.6000943209249</v>
+        <v>117.8802064943995</v>
       </c>
       <c r="C10" t="n">
-        <v>49.28828420649317</v>
+        <v>45.61238088514995</v>
       </c>
       <c r="D10" t="n">
-        <v>7.476337799261438</v>
+        <v>10.5628081802106</v>
       </c>
       <c r="E10" t="n">
-        <v>4.549383786126341</v>
+        <v>2.515587101244233</v>
       </c>
       <c r="F10" t="n">
-        <v>11.60810564566143</v>
+        <v>6.180082550112109</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05959084008124619</v>
+        <v>0.3622355638482634</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8091114962467111</v>
+        <v>-0.0701016074970305</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8802456601900024</v>
+        <v>-0.595029410979554</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8870248256119615</v>
+        <v>-0.08143030569272529</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.04060782180469721</v>
+        <v>-0.02258883652840354</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4965751809091302</v>
+        <v>-0.2523322578878389</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1067881451700619</v>
+        <v>-0.0427012840327172</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>79.91502332182849</v>
+        <v>89.82710780065112</v>
       </c>
       <c r="B11" t="n">
-        <v>135.6383473528533</v>
+        <v>103.3018683999195</v>
       </c>
       <c r="C11" t="n">
-        <v>45.66349429943531</v>
+        <v>48.15815748851574</v>
       </c>
       <c r="D11" t="n">
-        <v>8.604753095320422</v>
+        <v>7.208482793480274</v>
       </c>
       <c r="E11" t="n">
-        <v>4.404505748667284</v>
+        <v>2.206440779864022</v>
       </c>
       <c r="F11" t="n">
-        <v>11.13868971681955</v>
+        <v>13.28174692277464</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06882942097285696</v>
+        <v>0.04535155775525052</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7855426753228686</v>
+        <v>-0.8248648393894877</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8684550468364062</v>
+        <v>-0.8881871124972369</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8681763507252069</v>
+        <v>-0.8992870595956747</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1489079904579691</v>
+        <v>-0.0135520066922314</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.471970796683869</v>
+        <v>-0.5150181430796391</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1665812949296464</v>
+        <v>-0.004641369900507293</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>49.87807233937073</v>
+        <v>92.26916697185493</v>
       </c>
       <c r="B12" t="n">
-        <v>125.2708438969089</v>
+        <v>131.0084780987043</v>
       </c>
       <c r="C12" t="n">
-        <v>48.75926230542323</v>
+        <v>45.43001928459075</v>
       </c>
       <c r="D12" t="n">
-        <v>10.34364347821924</v>
+        <v>7.661181338034907</v>
       </c>
       <c r="E12" t="n">
-        <v>3.857190202629959</v>
+        <v>2.923392932495732</v>
       </c>
       <c r="F12" t="n">
-        <v>6.096138587288213</v>
+        <v>13.91527440485885</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3821234013492025</v>
+        <v>0.04154546237469248</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1555035851081176</v>
+        <v>-0.8375779272692696</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6211320484659927</v>
+        <v>-0.8947697873775889</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1880105142658784</v>
+        <v>-0.9088257142607208</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.03763272063904644</v>
+        <v>-0.1364372501936981</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2475926783701089</v>
+        <v>-0.5324178146744664</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.07562753838372795</v>
+        <v>-0.002913298456162922</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89.23632903043742</v>
+        <v>95.03991416308793</v>
       </c>
       <c r="B13" t="n">
-        <v>125.1227186107673</v>
+        <v>98.3418341509207</v>
       </c>
       <c r="C13" t="n">
-        <v>48.76344463954608</v>
+        <v>45.50274804011437</v>
       </c>
       <c r="D13" t="n">
-        <v>6.772961521470251</v>
+        <v>6.833854945140564</v>
       </c>
       <c r="E13" t="n">
-        <v>3.924099972275866</v>
+        <v>2.559142033762064</v>
       </c>
       <c r="F13" t="n">
-        <v>12.8807873500427</v>
+        <v>14.44869617763334</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04701833941376956</v>
+        <v>0.03760725701247531</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8433871292426701</v>
+        <v>-0.8506665704521331</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8979330129827076</v>
+        <v>-0.9017506250267655</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9130305638984729</v>
+        <v>-0.918415434779299</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.01003988228025142</v>
+        <v>-0.005008893211339575</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5416016003012688</v>
+        <v>-0.5521593884120015</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.07591006544863382</v>
+        <v>-0.01878139057040915</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>63.62753102823788</v>
+        <v>79.35944160462179</v>
       </c>
       <c r="B14" t="n">
-        <v>131.8341452094203</v>
+        <v>114.1981729114106</v>
       </c>
       <c r="C14" t="n">
-        <v>48.13966621592083</v>
+        <v>45.4938805437809</v>
       </c>
       <c r="D14" t="n">
-        <v>9.628984070739921</v>
+        <v>8.548719720001891</v>
       </c>
       <c r="E14" t="n">
-        <v>4.131532930757507</v>
+        <v>2.459780931964484</v>
       </c>
       <c r="F14" t="n">
-        <v>8.124453162631257</v>
+        <v>11.00361395826724</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1546542601259165</v>
+        <v>0.06904164125570569</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5862444011114362</v>
+        <v>-0.7507111481381955</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7797709383989083</v>
+        <v>-0.8517619118479505</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6851553405221692</v>
+        <v>-0.8393441348225167</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.09518614323282647</v>
+        <v>-0.04418957405527121</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3503020935248808</v>
+        <v>-0.4404360214329303</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.07107175436985129</v>
+        <v>-0.01684666409765001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>48.66479084927953</v>
+        <v>72.30126499546022</v>
       </c>
       <c r="B15" t="n">
-        <v>176.9372712735985</v>
+        <v>109.9074099740013</v>
       </c>
       <c r="C15" t="n">
-        <v>48.7867643229394</v>
+        <v>45.43113193747018</v>
       </c>
       <c r="D15" t="n">
-        <v>10.29467353007181</v>
+        <v>9.464837092504123</v>
       </c>
       <c r="E15" t="n">
-        <v>3.472361077397685</v>
+        <v>2.443502412512958</v>
       </c>
       <c r="F15" t="n">
-        <v>5.909667626700661</v>
+        <v>9.712156353628275</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4188756258197546</v>
+        <v>0.09587400089003305</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09218771142918744</v>
+        <v>-0.6737323958760739</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6001109152737462</v>
+        <v>-0.8167846991732121</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1061810101674366</v>
+        <v>-0.7705075113142232</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.01230611934690665</v>
+        <v>-0.1012461897737724</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2385293810370816</v>
+        <v>-0.390146513092654</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.07722978729931408</v>
+        <v>-0.003156059084402502</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>62.45996864121658</v>
+        <v>66.61346017010044</v>
       </c>
       <c r="B16" t="n">
-        <v>164.8478438150119</v>
+        <v>97.46074492668789</v>
       </c>
       <c r="C16" t="n">
-        <v>48.83288466568095</v>
+        <v>45.46758297459248</v>
       </c>
       <c r="D16" t="n">
-        <v>9.271038976236859</v>
+        <v>9.355114609096995</v>
       </c>
       <c r="E16" t="n">
-        <v>2.764552483308103</v>
+        <v>2.34234889457351</v>
       </c>
       <c r="F16" t="n">
-        <v>7.806019409805463</v>
+        <v>8.570074149510326</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1646945844785838</v>
+        <v>0.1279744039263559</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5638228968062505</v>
+        <v>-0.5913445072375706</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7707390818857732</v>
+        <v>-0.7830238969963571</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.662415113120317</v>
+        <v>-0.6915991869679409</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01819169643262323</v>
+        <v>-0.01375323739868957</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3415803210797762</v>
+        <v>-0.3621109274938595</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.08037946566442468</v>
+        <v>-0.01110901263835923</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>53.47935808660306</v>
+        <v>49.37993017718108</v>
       </c>
       <c r="B17" t="n">
-        <v>145.6794077496853</v>
+        <v>117.9294495755661</v>
       </c>
       <c r="C17" t="n">
-        <v>48.78065707662727</v>
+        <v>45.42694102211488</v>
       </c>
       <c r="D17" t="n">
-        <v>9.924758254329145</v>
+        <v>10.55581650749476</v>
       </c>
       <c r="E17" t="n">
-        <v>3.306311821516799</v>
+        <v>2.441742273747975</v>
       </c>
       <c r="F17" t="n">
-        <v>6.506562244386311</v>
+        <v>6.036574635590656</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2930028255411468</v>
+        <v>0.388354037304345</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3126933634537961</v>
+        <v>-0.017571910943396</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6756258919720869</v>
+        <v>-0.5781128179940253</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3825384058513328</v>
+        <v>-0.01187314498899772</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.008868025475269692</v>
+        <v>-0.004190313037211954</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2744945340193748</v>
+        <v>-0.2453494763288582</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.07681270753719055</v>
+        <v>-0.002241677552337201</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>73.26857919701003</v>
+        <v>71.18177850367979</v>
       </c>
       <c r="B18" t="n">
-        <v>153.1342912386641</v>
+        <v>146.3787383200482</v>
       </c>
       <c r="C18" t="n">
-        <v>48.78116102235428</v>
+        <v>45.43225835291232</v>
       </c>
       <c r="D18" t="n">
-        <v>8.52690894549691</v>
+        <v>9.348725362391988</v>
       </c>
       <c r="E18" t="n">
-        <v>4.352700452041026</v>
+        <v>2.160017009766997</v>
       </c>
       <c r="F18" t="n">
-        <v>9.67538896266524</v>
+        <v>9.45664621047365</v>
       </c>
       <c r="G18" t="n">
-        <v>0.09279465510475399</v>
+        <v>0.1011811523178164</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7252908203125301</v>
+        <v>-0.6587903208929106</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8400479570216849</v>
+        <v>-0.8103072468777665</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8170978330121047</v>
+        <v>-0.7564964267738143</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.05533121416210576</v>
+        <v>-0.05974134274622929</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4223213956153226</v>
+        <v>-0.3821701718387185</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.07684712330383951</v>
+        <v>-0.003401822453597408</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>68.37696380070204</v>
+        <v>55.96900312566029</v>
       </c>
       <c r="B19" t="n">
-        <v>135.0723276764204</v>
+        <v>110.1250117253144</v>
       </c>
       <c r="C19" t="n">
-        <v>48.78747485874596</v>
+        <v>45.47933919276714</v>
       </c>
       <c r="D19" t="n">
-        <v>8.75416120422647</v>
+        <v>10.11178125753859</v>
       </c>
       <c r="E19" t="n">
-        <v>4.062227511256756</v>
+        <v>4.376357301281081</v>
       </c>
       <c r="F19" t="n">
-        <v>8.760415095328197</v>
+        <v>6.911845481732311</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1185407008688215</v>
+        <v>0.2424319798931233</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6647503353929156</v>
+        <v>-0.3205341435815908</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8130621058847314</v>
+        <v>-0.6800690402939941</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7618825714378263</v>
+        <v>-0.3945607595372252</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.01072538044160421</v>
+        <v>-0.01768512802388051</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3857806875128522</v>
+        <v>-0.2947675234424522</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.07727831164073319</v>
+        <v>-0.01367400569464952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>54.9148689939197</v>
+        <v>57.09444627199501</v>
       </c>
       <c r="B20" t="n">
-        <v>177.2340798709917</v>
+        <v>110.5616400942005</v>
       </c>
       <c r="C20" t="n">
-        <v>48.78707733221543</v>
+        <v>45.42988452766944</v>
       </c>
       <c r="D20" t="n">
-        <v>9.891490475671883</v>
+        <v>10.05326567070128</v>
       </c>
       <c r="E20" t="n">
-        <v>2.635921996051798</v>
+        <v>2.075642088376763</v>
       </c>
       <c r="F20" t="n">
-        <v>6.716894454552031</v>
+        <v>7.074680432762376</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2654770472155662</v>
+        <v>0.2251377725162962</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3640791326088443</v>
+        <v>-0.359074806219535</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6941409352427872</v>
+        <v>-0.6938936401117232</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4430816289618887</v>
+        <v>-0.4397265573025941</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.02377358961916098</v>
+        <v>-0.000479346800251652</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.28521790059512</v>
+        <v>-0.2925031383639636</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.07725116351827087</v>
+        <v>-0.002883896946060394</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>85.42123102238276</v>
+        <v>50.1810368576726</v>
       </c>
       <c r="B21" t="n">
-        <v>169.3114662862132</v>
+        <v>117.5828099085269</v>
       </c>
       <c r="C21" t="n">
-        <v>47.26309433824107</v>
+        <v>45.42551639529843</v>
       </c>
       <c r="D21" t="n">
-        <v>7.417705781233575</v>
+        <v>10.54292220776019</v>
       </c>
       <c r="E21" t="n">
-        <v>3.391509611976513</v>
+        <v>2.518315872263253</v>
       </c>
       <c r="F21" t="n">
-        <v>12.09846231919665</v>
+        <v>6.14608705397575</v>
       </c>
       <c r="G21" t="n">
-        <v>0.05453030377383783</v>
+        <v>0.3655196998372122</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8227732735573972</v>
+        <v>-0.06308166477270669</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.88717947388701</v>
+        <v>-0.5927657337344931</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8975860358232524</v>
+        <v>-0.07222856432648889</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.04424931866282546</v>
+        <v>-0.01308552483709867</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.513102552154544</v>
+        <v>-0.2513577764325445</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.08073322234533727</v>
+        <v>-0.001930849883293867</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>59.12381618237376</v>
+        <v>69.7942959233894</v>
       </c>
       <c r="B22" t="n">
-        <v>177.9792220791583</v>
+        <v>132.2689551283121</v>
       </c>
       <c r="C22" t="n">
-        <v>48.83173319397435</v>
+        <v>45.42541417837509</v>
       </c>
       <c r="D22" t="n">
-        <v>9.586061201089603</v>
+        <v>9.431856245753268</v>
       </c>
       <c r="E22" t="n">
-        <v>3.173403062380324</v>
+        <v>2.13493624370555</v>
       </c>
       <c r="F22" t="n">
-        <v>7.315949546782118</v>
+        <v>9.200166873953563</v>
       </c>
       <c r="G22" t="n">
-        <v>0.201688717935782</v>
+        <v>0.1085127951328189</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4878892026561129</v>
+        <v>-0.638764000456014</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.740651043843817</v>
+        <v>-0.8017015545887606</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5822589024306194</v>
+        <v>-0.7373735010900062</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.02852534537964405</v>
+        <v>-0.05277517556039889</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3166590295825083</v>
+        <v>-0.3722843584541494</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.08030082866160267</v>
+        <v>-0.0019085480091105</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>49.47678873791041</v>
+        <v>96.50473955728003</v>
       </c>
       <c r="B23" t="n">
-        <v>184.6640126065812</v>
+        <v>118.668793106735</v>
       </c>
       <c r="C23" t="n">
-        <v>48.79635378138146</v>
+        <v>45.64056663857048</v>
       </c>
       <c r="D23" t="n">
-        <v>10.18655751930282</v>
+        <v>6.833854945140564</v>
       </c>
       <c r="E23" t="n">
-        <v>3.493270953927157</v>
+        <v>2.125211546830827</v>
       </c>
       <c r="F23" t="n">
-        <v>5.99484354202554</v>
+        <v>14.8504419569631</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3931010649094667</v>
+        <v>0.03580775305635199</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.135604586710099</v>
+        <v>-0.8568999691966274</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6145379202710928</v>
+        <v>-0.9050896133757234</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1625923301133106</v>
+        <v>-0.9228780002170058</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.002933207568757847</v>
+        <v>-0.05444928414352283</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2445950618857187</v>
+        <v>-0.5625962693456202</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.07788467640014632</v>
+        <v>-0.0488509029608318</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>50.67246375880221</v>
+        <v>62.25776902115238</v>
       </c>
       <c r="B24" t="n">
-        <v>122.3164480249619</v>
+        <v>110.6364604203469</v>
       </c>
       <c r="C24" t="n">
-        <v>48.80236669066447</v>
+        <v>45.65017662892971</v>
       </c>
       <c r="D24" t="n">
-        <v>10.0206447284863</v>
+        <v>10.15355716158815</v>
       </c>
       <c r="E24" t="n">
-        <v>3.478193639232229</v>
+        <v>4.522319830943289</v>
       </c>
       <c r="F24" t="n">
-        <v>6.158504134901646</v>
+        <v>7.982571100411855</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3580070413801227</v>
+        <v>0.1643612198993313</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1949639411959013</v>
+        <v>-0.4957717054264418</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6346756013324715</v>
+        <v>-0.7434648122094729</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2383087245914678</v>
+        <v>-0.5911690482634926</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.01027441587980174</v>
+        <v>-0.07758136339686982</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2646787975766804</v>
+        <v>-0.3185866042757107</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.07829531364077123</v>
+        <v>-0.05094762813011855</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>79.36373281841207</v>
+        <v>98.43008397813841</v>
       </c>
       <c r="B25" t="n">
-        <v>136.526315992773</v>
+        <v>110.7175686455313</v>
       </c>
       <c r="C25" t="n">
-        <v>47.62005234960609</v>
+        <v>45.47919759798201</v>
       </c>
       <c r="D25" t="n">
-        <v>8.307899984233561</v>
+        <v>7.434001144202727</v>
       </c>
       <c r="E25" t="n">
-        <v>3.626506633035757</v>
+        <v>4.338451255465504</v>
       </c>
       <c r="F25" t="n">
-        <v>10.93051948586203</v>
+        <v>15.52246693866193</v>
       </c>
       <c r="G25" t="n">
-        <v>0.07031988035926015</v>
+        <v>0.03369707385352306</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7814119606392416</v>
+        <v>-0.8644487331846962</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.866487066927521</v>
+        <v>-0.9091396367030046</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8648260315028692</v>
+        <v>-0.9281882618194142</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1125707814034757</v>
+        <v>-0.2496958189529004</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4678526181818944</v>
+        <v>-0.5763143483442361</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.08553754577090909</v>
+        <v>-0.01364311228698387</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>48.45192436858792</v>
+        <v>52.30664819042651</v>
       </c>
       <c r="B26" t="n">
-        <v>182.6624787885564</v>
+        <v>160.4902978983807</v>
       </c>
       <c r="C26" t="n">
-        <v>48.7867643229394</v>
+        <v>45.49014979715827</v>
       </c>
       <c r="D26" t="n">
-        <v>10.33042855809284</v>
+        <v>10.57774635235225</v>
       </c>
       <c r="E26" t="n">
-        <v>3.863764204078705</v>
+        <v>2.49613696078592</v>
       </c>
       <c r="F26" t="n">
-        <v>5.889638720797204</v>
+        <v>6.466297935194183</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4260302357188725</v>
+        <v>0.3131229941670058</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.08030045088306829</v>
+        <v>-0.1593188961251153</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.596192636219721</v>
+        <v>-0.6221989089617213</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0905722142932808</v>
+        <v>-0.1938778560180264</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.01619195829074736</v>
+        <v>-0.0140409764621564</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.2369392535831484</v>
+        <v>-0.2476848683567889</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.07722978729931408</v>
+        <v>-0.01603268301635166</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>93.24779585496222</v>
+        <v>90.81141124896665</v>
       </c>
       <c r="B27" t="n">
-        <v>135.1080847185695</v>
+        <v>98.21289987351953</v>
       </c>
       <c r="C27" t="n">
-        <v>48.10377025797542</v>
+        <v>42.4683902518311</v>
       </c>
       <c r="D27" t="n">
-        <v>7.593570627882161</v>
+        <v>7.673178373411407</v>
       </c>
       <c r="E27" t="n">
-        <v>3.331977805920717</v>
+        <v>2.262814592549272</v>
       </c>
       <c r="F27" t="n">
-        <v>14.12748286071274</v>
+        <v>13.56484008162636</v>
       </c>
       <c r="G27" t="n">
-        <v>0.04089675572038096</v>
+        <v>0.04378734854590784</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8613060501356861</v>
+        <v>-0.8301194842157734</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9074420024732676</v>
+        <v>-0.8908814872419741</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9258974797711907</v>
+        <v>-0.9032541748483687</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.303879020527873</v>
+        <v>-0.03989334771886738</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5715675371998115</v>
+        <v>-0.5220313051488874</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.07240614351809281</v>
+        <v>-0.2014845545634054</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>54.41388195656262</v>
+        <v>68.01384634616747</v>
       </c>
       <c r="B28" t="n">
-        <v>132.4604326195767</v>
+        <v>119.5592972134005</v>
       </c>
       <c r="C28" t="n">
-        <v>48.78696514157537</v>
+        <v>46.70086348407874</v>
       </c>
       <c r="D28" t="n">
-        <v>9.811031453332255</v>
+        <v>9.478006955862975</v>
       </c>
       <c r="E28" t="n">
-        <v>2.635921996051798</v>
+        <v>2.286499731083218</v>
       </c>
       <c r="F28" t="n">
-        <v>6.619811815787182</v>
+        <v>8.929896427201742</v>
       </c>
       <c r="G28" t="n">
-        <v>0.274421852378447</v>
+        <v>0.1192063403412188</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3469070644755118</v>
+        <v>-0.6104538296545727</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6879364662516085</v>
+        <v>-0.789709709930409</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4230547669417055</v>
+        <v>-0.709711756191336</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.0001413310292699671</v>
+        <v>-0.05848754565257269</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.2814754924922664</v>
+        <v>-0.3595986552164432</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.07724350172716547</v>
+        <v>-0.2801883965262698</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>84.54963141484848</v>
+        <v>63.65470413152563</v>
       </c>
       <c r="B29" t="n">
-        <v>158.7604294287717</v>
+        <v>132.1383943339279</v>
       </c>
       <c r="C29" t="n">
-        <v>48.78811775872639</v>
+        <v>45.64380910810827</v>
       </c>
       <c r="D29" t="n">
-        <v>7.291953724608114</v>
+        <v>9.661858136364192</v>
       </c>
       <c r="E29" t="n">
-        <v>4.039346552393894</v>
+        <v>2.452580271870136</v>
       </c>
       <c r="F29" t="n">
-        <v>11.86389296036739</v>
+        <v>8.109690512540732</v>
       </c>
       <c r="G29" t="n">
-        <v>0.05639576261322047</v>
+        <v>0.1510446495259491</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.8176078313346743</v>
+        <v>-0.5278660873803001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.8845592478256514</v>
+        <v>-0.7561756686465989</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.8936290801022941</v>
+        <v>-0.6254232091457415</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.01799336081969461</v>
+        <v>-0.003706490263724743</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.5065916423096742</v>
+        <v>-0.3285397669371202</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.07732221695537148</v>
+        <v>-0.04955835085998672</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>56.73414884799394</v>
+        <v>59.01068761154659</v>
       </c>
       <c r="B30" t="n">
-        <v>180.2647699035557</v>
+        <v>117.7521657336103</v>
       </c>
       <c r="C30" t="n">
-        <v>48.80238810649685</v>
+        <v>45.4255614346318</v>
       </c>
       <c r="D30" t="n">
-        <v>9.635648993379689</v>
+        <v>10.65927559073129</v>
       </c>
       <c r="E30" t="n">
-        <v>3.173403062380324</v>
+        <v>2.516150292278982</v>
       </c>
       <c r="F30" t="n">
-        <v>6.938430208235156</v>
+        <v>7.537630188026837</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2347629112484409</v>
+        <v>0.2005986755456378</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4222764581917003</v>
+        <v>-0.4097619538961791</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7156890895942946</v>
+        <v>-0.7106323003872506</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5097760503458726</v>
+        <v>-0.4960079366835499</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.0003327945865637184</v>
+        <v>-0.1159575488509605</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.2988080479633304</v>
+        <v>-0.2954511492322694</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.07829677618376008</v>
+        <v>-0.001940676646937506</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>77.96793752361114</v>
+        <v>87.01784016742511</v>
       </c>
       <c r="B31" t="n">
-        <v>166.7535351591882</v>
+        <v>114.5429316332342</v>
       </c>
       <c r="C31" t="n">
-        <v>49.78480758046175</v>
+        <v>45.42334373371948</v>
       </c>
       <c r="D31" t="n">
-        <v>8.016500858858279</v>
+        <v>8.043898688476091</v>
       </c>
       <c r="E31" t="n">
-        <v>3.262059805632309</v>
+        <v>2.065523283663091</v>
       </c>
       <c r="F31" t="n">
-        <v>10.56793552012206</v>
+        <v>12.67786673716658</v>
       </c>
       <c r="G31" t="n">
-        <v>0.07461331821671488</v>
+        <v>0.05047517363486433</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7701824545134769</v>
+        <v>-0.808316260536731</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8611020180505149</v>
+        <v>-0.8797488806249115</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8555809094275093</v>
+        <v>-0.8865144449183916</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.05723508822932089</v>
+        <v>-0.09548661210180072</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.4574259300010088</v>
+        <v>-0.4950021111929038</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.09567629732605898</v>
+        <v>-0.001456814629706149</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>50.67246375880221</v>
+        <v>53.11752946222487</v>
       </c>
       <c r="B32" t="n">
-        <v>131.6218261413431</v>
+        <v>160.4902978983807</v>
       </c>
       <c r="C32" t="n">
-        <v>48.80236669066447</v>
+        <v>45.42975941301653</v>
       </c>
       <c r="D32" t="n">
-        <v>10.08521543214985</v>
+        <v>10.57916257215382</v>
       </c>
       <c r="E32" t="n">
-        <v>3.490715095455297</v>
+        <v>2.49613696078592</v>
       </c>
       <c r="F32" t="n">
-        <v>6.13773658174446</v>
+        <v>6.584049554540453</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3589871075045149</v>
+        <v>0.2956347066085417</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1944552872050462</v>
+        <v>-0.1965377787342367</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6344103188459054</v>
+        <v>-0.6348139793693069</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2375308943340135</v>
+        <v>-0.2409510628330079</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.0001621362190852037</v>
+        <v>-0.02385516850348922</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.2535268376661283</v>
+        <v>-0.2534623974183522</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.07829531364077123</v>
+        <v>-0.002856599203605314</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>56.73414884799394</v>
+        <v>52.01696895282264</v>
       </c>
       <c r="B33" t="n">
-        <v>163.7141312890088</v>
+        <v>153.1610007492178</v>
       </c>
       <c r="C33" t="n">
-        <v>48.80238810649685</v>
+        <v>45.47170576674186</v>
       </c>
       <c r="D33" t="n">
-        <v>9.635648993379689</v>
+        <v>10.57916257215382</v>
       </c>
       <c r="E33" t="n">
-        <v>3.173403062380324</v>
+        <v>2.442163250240553</v>
       </c>
       <c r="F33" t="n">
-        <v>6.938430208235156</v>
+        <v>6.422869100110809</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2347629112484409</v>
+        <v>0.3196727353145812</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4222764581917003</v>
+        <v>-0.1454732153122328</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7156890895942946</v>
+        <v>-0.6175499719116145</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5097760503458726</v>
+        <v>-0.1761914963833846</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.0003327945865637184</v>
+        <v>-0.01003900948614264</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.2988080479633304</v>
+        <v>-0.2456209037888613</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.07829677618376008</v>
+        <v>-0.01200853092549803</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>47.84130480513049</v>
+        <v>60.66002902095099</v>
       </c>
       <c r="B34" t="n">
-        <v>170.6094786001775</v>
+        <v>103.4503392470804</v>
       </c>
       <c r="C34" t="n">
-        <v>48.83274662596381</v>
+        <v>45.64380910810827</v>
       </c>
       <c r="D34" t="n">
-        <v>10.47861953308137</v>
+        <v>9.661858136364192</v>
       </c>
       <c r="E34" t="n">
-        <v>2.547542631886976</v>
+        <v>2.118888500977041</v>
       </c>
       <c r="F34" t="n">
-        <v>5.846833288197844</v>
+        <v>7.583388898818553</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4477313051706346</v>
+        <v>0.1798212800273031</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.04487076238897411</v>
+        <v>-0.4632804478842325</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5845770166315643</v>
+        <v>-0.7325338669818624</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.04361851443818299</v>
+        <v>-0.5572989337296705</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.03649157882086095</v>
+        <v>-0.006860315893941392</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.2323778828656556</v>
+        <v>-0.3299502176571324</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.08037003857249979</v>
+        <v>-0.04955835085998672</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>97.55785416459517</v>
+        <v>56.40806097831584</v>
       </c>
       <c r="B35" t="n">
-        <v>162.1168756020153</v>
+        <v>110.1250117253144</v>
       </c>
       <c r="C35" t="n">
-        <v>47.55244860465032</v>
+        <v>45.43478913704248</v>
       </c>
       <c r="D35" t="n">
-        <v>6.019725461372156</v>
+        <v>10.11178125753859</v>
       </c>
       <c r="E35" t="n">
-        <v>2.563621857593814</v>
+        <v>4.300327813539116</v>
       </c>
       <c r="F35" t="n">
-        <v>14.86960784688666</v>
+        <v>6.979165715039737</v>
       </c>
       <c r="G35" t="n">
-        <v>0.03508880962369159</v>
+        <v>0.2355237316738513</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8779067251928161</v>
+        <v>-0.3359193840121928</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9167009790105358</v>
+        <v>-0.685557434231978</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9373928491196164</v>
+        <v>-0.412691738238868</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.05766207116261229</v>
+        <v>-0.001785020345718274</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.6037639733128785</v>
+        <v>-0.2874839459039346</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.08639696069218107</v>
+        <v>-0.003953993536540829</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>59.65713848925377</v>
+        <v>81.17348754711689</v>
       </c>
       <c r="B36" t="n">
-        <v>183.8271825729396</v>
+        <v>99.86410071235866</v>
       </c>
       <c r="C36" t="n">
-        <v>48.80236669066447</v>
+        <v>45.50274804011437</v>
       </c>
       <c r="D36" t="n">
-        <v>10.02111701427179</v>
+        <v>8.415806895418688</v>
       </c>
       <c r="E36" t="n">
-        <v>3.470328605793829</v>
+        <v>2.159622284309255</v>
       </c>
       <c r="F36" t="n">
-        <v>7.512727554481329</v>
+        <v>11.38305890304095</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1959782407815361</v>
+        <v>0.06388028503247796</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5006184661398153</v>
+        <v>-0.7663366109942109</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7454838874625085</v>
+        <v>-0.8591725099694947</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5958822914789939</v>
+        <v>-0.8525344489693548</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.1180333424611794</v>
+        <v>-0.05214434094811417</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.3206429844034346</v>
+        <v>-0.453361098773208</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.07829531364077123</v>
+        <v>-0.01878139057040915</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>96.26790792932238</v>
+        <v>83.41264423649051</v>
       </c>
       <c r="B37" t="n">
-        <v>162.9915117700931</v>
+        <v>110.5561912154054</v>
       </c>
       <c r="C37" t="n">
-        <v>48.78280209303479</v>
+        <v>45.42988018857561</v>
       </c>
       <c r="D37" t="n">
-        <v>6.075221384934339</v>
+        <v>8.04820216234998</v>
       </c>
       <c r="E37" t="n">
-        <v>2.492208918229485</v>
+        <v>2.05821142880077</v>
       </c>
       <c r="F37" t="n">
-        <v>14.53155476755195</v>
+        <v>11.81056897019191</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0366223049444887</v>
+        <v>0.05814054475551379</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.873323421581213</v>
+        <v>-0.7838916569776543</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9141488651884072</v>
+        <v>-0.867679459979584</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9342749951163239</v>
+        <v>-0.867022209997114</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.04726746911455829</v>
+        <v>-0.01364753028507736</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.5941279849875166</v>
+        <v>-0.469315090184995</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.0769591962961623</v>
+        <v>-0.002882950234678744</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>90.69914167620855</v>
+        <v>58.84206085205808</v>
       </c>
       <c r="B38" t="n">
-        <v>158.2736909791344</v>
+        <v>122.6707709751847</v>
       </c>
       <c r="C38" t="n">
-        <v>48.79423070620024</v>
+        <v>45.4255614346318</v>
       </c>
       <c r="D38" t="n">
-        <v>6.772961521470251</v>
+        <v>10.65927559073129</v>
       </c>
       <c r="E38" t="n">
-        <v>3.481041957956093</v>
+        <v>2.131044213942614</v>
       </c>
       <c r="F38" t="n">
-        <v>13.24609684670379</v>
+        <v>7.509535216523373</v>
       </c>
       <c r="G38" t="n">
-        <v>0.04457072260224066</v>
+        <v>0.2027124273650766</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8503527003845749</v>
+        <v>-0.4047998662994624</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.901624077272088</v>
+        <v>-0.7087870671750388</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9180997226513407</v>
+        <v>-0.4903758738462227</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.05700280461662655</v>
+        <v>-0.1137372010016501</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.5525289127670178</v>
+        <v>-0.2942496835709137</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.07773968606468297</v>
+        <v>-0.001940676646937506</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>63.47516002959358</v>
+        <v>53.04601874466017</v>
       </c>
       <c r="B39" t="n">
-        <v>132.1135972998438</v>
+        <v>117.5828099085269</v>
       </c>
       <c r="C39" t="n">
-        <v>48.77390620494953</v>
+        <v>45.42963257815095</v>
       </c>
       <c r="D39" t="n">
-        <v>9.597194270662619</v>
+        <v>10.54292220776019</v>
       </c>
       <c r="E39" t="n">
-        <v>3.090848226442233</v>
+        <v>2.518298385400437</v>
       </c>
       <c r="F39" t="n">
-        <v>8.071818038472776</v>
+        <v>6.564419123067703</v>
       </c>
       <c r="G39" t="n">
-        <v>0.155862449994257</v>
+        <v>0.2970110324717226</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.5834468779615919</v>
+        <v>-0.1934229397283287</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.77864612379223</v>
+        <v>-0.6337651770868985</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.6823452461141193</v>
+        <v>-0.2370563199206044</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.09858884279490798</v>
+        <v>-0.01618813738885722</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.3491638715401874</v>
+        <v>-0.2529528835557038</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.07651592988255317</v>
+        <v>-0.002828926142025706</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>92.22445542430806</v>
+        <v>64.79759225765795</v>
       </c>
       <c r="B40" t="n">
-        <v>135.1080847185695</v>
+        <v>131.647333887829</v>
       </c>
       <c r="C40" t="n">
-        <v>48.79417877421365</v>
+        <v>45.43005475997703</v>
       </c>
       <c r="D40" t="n">
-        <v>6.772961521470251</v>
+        <v>9.881052809378893</v>
       </c>
       <c r="E40" t="n">
-        <v>3.323044266576107</v>
+        <v>2.011949117914149</v>
       </c>
       <c r="F40" t="n">
-        <v>13.63764973506985</v>
+        <v>8.35985437364754</v>
       </c>
       <c r="G40" t="n">
-        <v>0.04220855308980986</v>
+        <v>0.1418909851767148</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.8571560556750889</v>
+        <v>-0.5515099833550074</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9052680605467277</v>
+        <v>-0.7655613942663783</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9229769832313788</v>
+        <v>-0.650063294820918</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.1053084422789929</v>
+        <v>-0.06036388987928656</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.5639231128253577</v>
+        <v>-0.3366828448358129</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.07773613949401777</v>
+        <v>-0.002921038540443927</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>61.52921293878697</v>
+        <v>65.87620620866275</v>
       </c>
       <c r="B41" t="n">
-        <v>131.6124211640772</v>
+        <v>98.3576329334053</v>
       </c>
       <c r="C41" t="n">
-        <v>48.79114056177918</v>
+        <v>45.43120704402001</v>
       </c>
       <c r="D41" t="n">
-        <v>9.518044405446931</v>
+        <v>9.428561148038876</v>
       </c>
       <c r="E41" t="n">
-        <v>3.590496743611212</v>
+        <v>2.448664768329503</v>
       </c>
       <c r="F41" t="n">
-        <v>7.704133086624105</v>
+        <v>8.448165284187636</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1742865292935804</v>
+        <v>0.1332343318104961</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.5441183870689569</v>
+        <v>-0.5779128886047719</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7627666068268355</v>
+        <v>-0.7775395110369764</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6419979202250499</v>
+        <v>-0.6780900828125163</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.05257186587785201</v>
+        <v>-0.01554064715930637</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.3346275110810873</v>
+        <v>-0.3567197579008463</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.07752865205128393</v>
+        <v>-0.003172445968002008</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>53.85373371348113</v>
+        <v>58.04604940181235</v>
       </c>
       <c r="B42" t="n">
-        <v>159.0582400133238</v>
+        <v>110.7175686455313</v>
       </c>
       <c r="C42" t="n">
-        <v>48.78652130010283</v>
+        <v>45.47933919276714</v>
       </c>
       <c r="D42" t="n">
-        <v>9.891490475671883</v>
+        <v>10.11178125753859</v>
       </c>
       <c r="E42" t="n">
-        <v>3.658919776002146</v>
+        <v>4.338451255465504</v>
       </c>
       <c r="F42" t="n">
-        <v>6.554894923622388</v>
+        <v>7.246634150731833</v>
       </c>
       <c r="G42" t="n">
-        <v>0.285406370707096</v>
+        <v>0.212019054556281</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.3266630045382865</v>
+        <v>-0.3813912403499535</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.6806268740980185</v>
+        <v>-0.7002955896989094</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.3991596463271167</v>
+        <v>-0.4637639447746779</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.007919222150209713</v>
+        <v>-0.00499434983149068</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.277291146057344</v>
+        <v>-0.288578101987913</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.0772131906366474</v>
+        <v>-0.01367400569464952</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>47.84130480513049</v>
+        <v>85.49989626302276</v>
       </c>
       <c r="B43" t="n">
-        <v>125.2962967034327</v>
+        <v>104.3439355413496</v>
       </c>
       <c r="C43" t="n">
-        <v>48.83274662596381</v>
+        <v>46.83484769109002</v>
       </c>
       <c r="D43" t="n">
-        <v>10.47861953308137</v>
+        <v>7.734074208913186</v>
       </c>
       <c r="E43" t="n">
-        <v>2.523575192084813</v>
+        <v>2.851805811563848</v>
       </c>
       <c r="F43" t="n">
-        <v>5.879808871365839</v>
+        <v>12.29060799829186</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4467739247366476</v>
+        <v>0.05349945286120595</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.04533540937067208</v>
+        <v>-0.798551063347293</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5848091647235358</v>
+        <v>-0.8748869374987789</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.04437834017944257</v>
+        <v>-0.8788159533532012</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.05766360111763887</v>
+        <v>-0.0142700289014476</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.2436051601278035</v>
+        <v>-0.4841867608740371</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.08037003857249979</v>
+        <v>-0.30942131441964</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>70.14834877207892</v>
+        <v>87.01784016742511</v>
       </c>
       <c r="B44" t="n">
-        <v>177.2557733500772</v>
+        <v>119.9763566592435</v>
       </c>
       <c r="C44" t="n">
-        <v>48.78163471350114</v>
+        <v>45.42334373371948</v>
       </c>
       <c r="D44" t="n">
-        <v>8.683992358198804</v>
+        <v>8.043898688476091</v>
       </c>
       <c r="E44" t="n">
-        <v>3.134651712224037</v>
+        <v>2.025668764966083</v>
       </c>
       <c r="F44" t="n">
-        <v>9.086880540767192</v>
+        <v>12.67786673716658</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1082279986732182</v>
+        <v>0.05047517363486433</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.6886134187836906</v>
+        <v>-0.808316260536731</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.8235292099376951</v>
+        <v>-0.8797488806249115</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.7840743216329459</v>
+        <v>-0.8865144449183916</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.02883219717802213</v>
+        <v>-0.09548661210180072</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.3990130567676058</v>
+        <v>-0.4950021111929038</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.07687947290638596</v>
+        <v>-0.001456814629706149</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>92.91677926783818</v>
+        <v>57.94979594238078</v>
       </c>
       <c r="B45" t="n">
-        <v>157.8491137643977</v>
+        <v>120.2445033842656</v>
       </c>
       <c r="C45" t="n">
-        <v>48.79417877421365</v>
+        <v>45.4335134729502</v>
       </c>
       <c r="D45" t="n">
-        <v>6.827352896632662</v>
+        <v>10.10712488725078</v>
       </c>
       <c r="E45" t="n">
-        <v>3.314006237553381</v>
+        <v>2.438749913728403</v>
       </c>
       <c r="F45" t="n">
-        <v>13.83119293063391</v>
+        <v>7.227205353319606</v>
       </c>
       <c r="G45" t="n">
-        <v>0.04120497323672141</v>
+        <v>0.2132834950681723</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.8600899521129026</v>
+        <v>-0.3784010278755447</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.9068480326582411</v>
+        <v>-0.6992026089212716</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.9250562448745027</v>
+        <v>-0.4603249094653009</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.1410579439267984</v>
+        <v>-0.001678923158498987</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.5690948202122281</v>
+        <v>-0.2878922960894631</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.07773613949401777</v>
+        <v>-0.003675666825496832</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>70.14834877207892</v>
+        <v>74.04923834716537</v>
       </c>
       <c r="B46" t="n">
-        <v>132.1135972998438</v>
+        <v>120.1794103939494</v>
       </c>
       <c r="C46" t="n">
-        <v>48.78163471350114</v>
+        <v>45.42330356526791</v>
       </c>
       <c r="D46" t="n">
-        <v>8.683992358198804</v>
+        <v>9.118983834788684</v>
       </c>
       <c r="E46" t="n">
-        <v>3.134651712224037</v>
+        <v>2.035075792874224</v>
       </c>
       <c r="F46" t="n">
-        <v>9.086880540767192</v>
+        <v>9.98857579031732</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1082279986732182</v>
+        <v>0.08798180604794539</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.6886134187836906</v>
+        <v>-0.6956348174079336</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8235292099376951</v>
+        <v>-0.8265129452728091</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.7840743216329459</v>
+        <v>-0.7907167310736289</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.02883219717802213</v>
+        <v>-0.06316804327092387</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.3990130567676058</v>
+        <v>-0.4026008232235532</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.07687947290638596</v>
+        <v>-0.001448050603908568</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>94.3977602283653</v>
+        <v>60.73066467738907</v>
       </c>
       <c r="B47" t="n">
-        <v>135.1080847185695</v>
+        <v>102.9638919504679</v>
       </c>
       <c r="C47" t="n">
-        <v>48.96594273311854</v>
+        <v>45.64380910810827</v>
       </c>
       <c r="D47" t="n">
-        <v>7.593570627882161</v>
+        <v>9.661858136364192</v>
       </c>
       <c r="E47" t="n">
-        <v>3.331977805920717</v>
+        <v>2.118888500977041</v>
       </c>
       <c r="F47" t="n">
-        <v>14.41972457580223</v>
+        <v>7.595510828636522</v>
       </c>
       <c r="G47" t="n">
-        <v>0.03929183052679255</v>
+        <v>0.1790622137044951</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.8659633347693027</v>
+        <v>-0.4650989076911412</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.9099844798099789</v>
+        <v>-0.7332249662422876</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.9291637345542586</v>
+        <v>-0.5592872565900732</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.3449723932269014</v>
+        <v>-0.008044883617947095</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.5801578512560798</v>
+        <v>-0.330479985080418</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.08918412680294496</v>
+        <v>-0.04955835085998672</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>87.45697461149695</v>
+        <v>64.04250863155829</v>
       </c>
       <c r="B48" t="n">
-        <v>127.0560828719292</v>
+        <v>131.647333887829</v>
       </c>
       <c r="C48" t="n">
-        <v>48.78051505564756</v>
+        <v>45.43005475997703</v>
       </c>
       <c r="D48" t="n">
-        <v>6.964672151070191</v>
+        <v>10.04775906646447</v>
       </c>
       <c r="E48" t="n">
-        <v>2.35974140583097</v>
+        <v>2.069076117679109</v>
       </c>
       <c r="F48" t="n">
-        <v>12.48318607483146</v>
+        <v>8.263217635270285</v>
       </c>
       <c r="G48" t="n">
-        <v>0.05029682571583748</v>
+        <v>0.1482102562643351</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.8342462217352451</v>
+        <v>-0.5357825451582146</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.8931351330307334</v>
+        <v>-0.7592373659556381</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9062627079037757</v>
+        <v>-0.6336644953985162</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.01070281810384089</v>
+        <v>-0.08002390439411912</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.528309698717506</v>
+        <v>-0.3313028739998528</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.07680300855447267</v>
+        <v>-0.002921038540443927</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>71.76546540431326</v>
+        <v>95.30675381171015</v>
       </c>
       <c r="B49" t="n">
-        <v>126.2454174118332</v>
+        <v>93.2263528345587</v>
       </c>
       <c r="C49" t="n">
-        <v>48.78146368537328</v>
+        <v>45.42615060975846</v>
       </c>
       <c r="D49" t="n">
-        <v>8.557178102152875</v>
+        <v>8.046895665401587</v>
       </c>
       <c r="E49" t="n">
-        <v>4.399115514469022</v>
+        <v>2.531313096215456</v>
       </c>
       <c r="F49" t="n">
-        <v>9.377073213922525</v>
+        <v>14.81523542920147</v>
       </c>
       <c r="G49" t="n">
-        <v>0.09979460057541617</v>
+        <v>0.03746748380288535</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.7084384774466843</v>
+        <v>-0.851577535495266</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.8323976392875169</v>
+        <v>-0.9021379033978475</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.8020973605973618</v>
+        <v>-0.9190440633662964</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.03208436752101524</v>
+        <v>-0.2868845053119163</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.4110930307718427</v>
+        <v>-0.5540606209084348</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.07686779294994696</v>
+        <v>-0.002069223947300525</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>67.42270464490677</v>
+        <v>68.51721415882385</v>
       </c>
       <c r="B50" t="n">
-        <v>132.1135972998438</v>
+        <v>117.6860028386616</v>
       </c>
       <c r="C50" t="n">
-        <v>48.77390620494953</v>
+        <v>46.73387742085057</v>
       </c>
       <c r="D50" t="n">
-        <v>8.88844138140877</v>
+        <v>9.483477864919536</v>
       </c>
       <c r="E50" t="n">
-        <v>3.158384859322643</v>
+        <v>2.513212037216738</v>
       </c>
       <c r="F50" t="n">
-        <v>8.618419010813728</v>
+        <v>9.03012493831082</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1247782388988321</v>
+        <v>0.1161371604942415</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.6507526054986575</v>
+        <v>-0.6186754736476767</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8069922126909501</v>
+        <v>-0.793147673608927</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.7486029149222688</v>
+        <v>-0.7178023158676287</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.02242374943161363</v>
+        <v>-0.06835574802637362</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.3786523050786273</v>
+        <v>-0.3631851508816198</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.07651592988255317</v>
+        <v>-0.2873914372764882</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>60.02746971184641</v>
+        <v>61.67636223974248</v>
       </c>
       <c r="B51" t="n">
-        <v>123.1077853135243</v>
+        <v>139.3185181828905</v>
       </c>
       <c r="C51" t="n">
-        <v>48.8023637169234</v>
+        <v>45.42581167113932</v>
       </c>
       <c r="D51" t="n">
-        <v>10.3463396438785</v>
+        <v>9.926028337112289</v>
       </c>
       <c r="E51" t="n">
-        <v>4.383258164793165</v>
+        <v>2.39689499969438</v>
       </c>
       <c r="F51" t="n">
-        <v>7.65665489282854</v>
+        <v>7.812589692858324</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1921862484790879</v>
+        <v>0.1696272932131299</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.5091724214689912</v>
+        <v>-0.4821167527399455</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7487445608700984</v>
+        <v>-0.738244847956534</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.604969581453029</v>
+        <v>-0.5764796559861907</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.177496041368632</v>
+        <v>-0.02140151956127877</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.3234093844593757</v>
+        <v>-0.3144440809581651</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.07829511055624613</v>
+        <v>-0.001995273703124245</v>
       </c>
     </row>
   </sheetData>
